--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402167</v>
+        <v>121402250</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>97987</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R2" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402206</v>
+        <v>121402140</v>
       </c>
       <c r="B3" t="n">
-        <v>98102</v>
+        <v>105171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R3" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402236</v>
+        <v>121402165</v>
       </c>
       <c r="B4" t="n">
-        <v>97985</v>
+        <v>98102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R4" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402168</v>
+        <v>121402167</v>
       </c>
       <c r="B5" t="n">
-        <v>98083</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,20 +993,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402238</v>
+        <v>121402169</v>
       </c>
       <c r="B6" t="n">
-        <v>98001</v>
+        <v>97999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,30 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R6" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1149,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402178</v>
+        <v>121402212</v>
       </c>
       <c r="B7" t="n">
-        <v>99092</v>
+        <v>97999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222467</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R7" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1251,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402171</v>
+        <v>121402192</v>
       </c>
       <c r="B8" t="n">
-        <v>97991</v>
+        <v>105171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223572</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R8" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1353,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402192</v>
+        <v>121402236</v>
       </c>
       <c r="B9" t="n">
-        <v>105171</v>
+        <v>97985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402164</v>
+        <v>121402177</v>
       </c>
       <c r="B10" t="n">
-        <v>97985</v>
+        <v>99120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>222662</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402170</v>
+        <v>121402168</v>
       </c>
       <c r="B11" t="n">
-        <v>98001</v>
+        <v>98083</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,19 +1609,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1687,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402165</v>
+        <v>121402199</v>
       </c>
       <c r="B12" t="n">
-        <v>98102</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1703,34 +1711,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R12" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1757,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402166</v>
+        <v>121402164</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>97985</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1805,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402140</v>
+        <v>121402171</v>
       </c>
       <c r="B14" t="n">
-        <v>105171</v>
+        <v>97991</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1907,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402191</v>
+        <v>121402166</v>
       </c>
       <c r="B15" t="n">
-        <v>97035</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2009,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2095,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402199</v>
+        <v>121402206</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98102</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402250</v>
+        <v>121402191</v>
       </c>
       <c r="B17" t="n">
-        <v>97987</v>
+        <v>97035</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2213,16 +2221,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2233,14 +2241,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R17" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2267,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402177</v>
+        <v>121402220</v>
       </c>
       <c r="B18" t="n">
-        <v>99120</v>
+        <v>97035</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2315,16 +2323,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222662</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2335,14 +2343,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R18" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2369,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2401,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402220</v>
+        <v>121402178</v>
       </c>
       <c r="B19" t="n">
-        <v>97035</v>
+        <v>99092</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2417,34 +2425,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>222467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R19" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2471,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402250</v>
+        <v>121402236</v>
       </c>
       <c r="B2" t="n">
-        <v>97987</v>
+        <v>97998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>504</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402140</v>
+        <v>121402170</v>
       </c>
       <c r="B3" t="n">
-        <v>105171</v>
+        <v>98014</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,23 +793,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -879,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402165</v>
+        <v>121402250</v>
       </c>
       <c r="B4" t="n">
-        <v>98102</v>
+        <v>98000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +891,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R4" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402167</v>
+        <v>121402199</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +989,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R5" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1051,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402169</v>
+        <v>121402238</v>
       </c>
       <c r="B6" t="n">
-        <v>97999</v>
+        <v>98014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1095,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R6" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1153,12 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402212</v>
+        <v>121402191</v>
       </c>
       <c r="B7" t="n">
-        <v>97999</v>
+        <v>97048</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1193,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R7" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1255,12 +1247,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402192</v>
+        <v>121402178</v>
       </c>
       <c r="B8" t="n">
-        <v>105171</v>
+        <v>99105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1295,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>222467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R8" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1357,12 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402236</v>
+        <v>121402164</v>
       </c>
       <c r="B9" t="n">
-        <v>97985</v>
+        <v>97998</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,14 +1417,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R9" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1459,12 +1451,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402177</v>
+        <v>121402206</v>
       </c>
       <c r="B10" t="n">
-        <v>99120</v>
+        <v>98115</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222662</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R10" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1561,12 +1553,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402168</v>
+        <v>121402220</v>
       </c>
       <c r="B11" t="n">
-        <v>98083</v>
+        <v>97048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1601,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R11" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1663,12 +1655,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402199</v>
+        <v>121402171</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,34 +1703,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>223572</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R12" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1765,12 +1757,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402164</v>
+        <v>121402140</v>
       </c>
       <c r="B13" t="n">
-        <v>97985</v>
+        <v>105184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1805,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402171</v>
+        <v>121402167</v>
       </c>
       <c r="B14" t="n">
-        <v>97991</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1903,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223572</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2001,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402166</v>
+        <v>121402192</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>105184</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,34 +2009,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R15" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2071,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402206</v>
+        <v>121402165</v>
       </c>
       <c r="B16" t="n">
-        <v>98102</v>
+        <v>98115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,14 +2131,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R16" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2173,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402191</v>
+        <v>121402177</v>
       </c>
       <c r="B17" t="n">
-        <v>97035</v>
+        <v>99133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,16 +2213,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>222662</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2307,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402220</v>
+        <v>121402166</v>
       </c>
       <c r="B18" t="n">
-        <v>97035</v>
+        <v>98117</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,34 +2315,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R18" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2377,12 +2369,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402178</v>
+        <v>121402168</v>
       </c>
       <c r="B19" t="n">
-        <v>99092</v>
+        <v>98096</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222467</v>
+        <v>219811</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402236</v>
+        <v>121402168</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>98097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R2" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402170</v>
+        <v>121402166</v>
       </c>
       <c r="B3" t="n">
-        <v>98014</v>
+        <v>98118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,19 +793,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402250</v>
+        <v>121402192</v>
       </c>
       <c r="B4" t="n">
-        <v>98000</v>
+        <v>105185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402199</v>
+        <v>121402164</v>
       </c>
       <c r="B5" t="n">
-        <v>98117</v>
+        <v>97999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R5" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1047,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402238</v>
+        <v>121402191</v>
       </c>
       <c r="B6" t="n">
-        <v>98014</v>
+        <v>97049</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,30 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R6" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1145,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402191</v>
+        <v>121402140</v>
       </c>
       <c r="B7" t="n">
-        <v>97048</v>
+        <v>105185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1193,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402178</v>
+        <v>121402238</v>
       </c>
       <c r="B8" t="n">
-        <v>99105</v>
+        <v>98015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1295,34 +1303,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222467</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R8" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1349,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402164</v>
+        <v>121402177</v>
       </c>
       <c r="B9" t="n">
-        <v>97998</v>
+        <v>99134</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>222662</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402206</v>
+        <v>121402178</v>
       </c>
       <c r="B10" t="n">
-        <v>98115</v>
+        <v>99106</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1499,34 +1503,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R10" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1553,12 +1557,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402220</v>
+        <v>121402199</v>
       </c>
       <c r="B11" t="n">
-        <v>97048</v>
+        <v>98118</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1601,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402171</v>
+        <v>121402165</v>
       </c>
       <c r="B12" t="n">
-        <v>98004</v>
+        <v>98116</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1703,21 +1707,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223572</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402140</v>
+        <v>121402236</v>
       </c>
       <c r="B13" t="n">
-        <v>105184</v>
+        <v>97999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1805,34 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R13" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1859,12 +1863,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402167</v>
+        <v>121402220</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>97049</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1903,38 +1907,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R14" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1961,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1993,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402192</v>
+        <v>121402170</v>
       </c>
       <c r="B15" t="n">
-        <v>105184</v>
+        <v>98015</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2009,34 +2013,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>223597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R15" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402165</v>
+        <v>121402206</v>
       </c>
       <c r="B16" t="n">
-        <v>98115</v>
+        <v>98116</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R16" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402177</v>
+        <v>121402250</v>
       </c>
       <c r="B17" t="n">
-        <v>99133</v>
+        <v>98001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2213,16 +2213,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222662</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2233,14 +2233,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R17" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402166</v>
+        <v>121402167</v>
       </c>
       <c r="B18" t="n">
-        <v>98117</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2311,25 +2311,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402168</v>
+        <v>121402171</v>
       </c>
       <c r="B19" t="n">
-        <v>98096</v>
+        <v>98005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219811</v>
+        <v>223572</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402168</v>
+        <v>121402212</v>
       </c>
       <c r="B2" t="n">
-        <v>98097</v>
+        <v>98016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R2" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402166</v>
+        <v>121402178</v>
       </c>
       <c r="B3" t="n">
-        <v>98118</v>
+        <v>99109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>222467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402192</v>
+        <v>121402206</v>
       </c>
       <c r="B4" t="n">
-        <v>105185</v>
+        <v>98119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402164</v>
+        <v>121402192</v>
       </c>
       <c r="B5" t="n">
-        <v>97999</v>
+        <v>105188</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R5" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402191</v>
+        <v>121402166</v>
       </c>
       <c r="B6" t="n">
-        <v>97049</v>
+        <v>98121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402140</v>
+        <v>121402168</v>
       </c>
       <c r="B7" t="n">
-        <v>105185</v>
+        <v>98100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402238</v>
+        <v>121402191</v>
       </c>
       <c r="B8" t="n">
-        <v>98015</v>
+        <v>97052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,30 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R8" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1353,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402177</v>
+        <v>121402164</v>
       </c>
       <c r="B9" t="n">
-        <v>99134</v>
+        <v>98002</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222662</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402178</v>
+        <v>121402171</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>98008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222467</v>
+        <v>223572</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402199</v>
+        <v>121402167</v>
       </c>
       <c r="B11" t="n">
-        <v>98118</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1601,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R11" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1659,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402165</v>
+        <v>121402177</v>
       </c>
       <c r="B12" t="n">
-        <v>98116</v>
+        <v>99137</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>222662</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402236</v>
+        <v>121402140</v>
       </c>
       <c r="B13" t="n">
-        <v>97999</v>
+        <v>105188</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R13" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1863,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1895,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402220</v>
+        <v>121402165</v>
       </c>
       <c r="B14" t="n">
-        <v>97049</v>
+        <v>98119</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R14" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402170</v>
+        <v>121402220</v>
       </c>
       <c r="B15" t="n">
-        <v>98015</v>
+        <v>97052</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,30 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R15" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2063,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402206</v>
+        <v>121402170</v>
       </c>
       <c r="B16" t="n">
-        <v>98116</v>
+        <v>98018</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,34 +2119,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R16" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2165,12 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402250</v>
+        <v>121402236</v>
       </c>
       <c r="B17" t="n">
-        <v>98001</v>
+        <v>98002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2213,21 +2217,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>220093</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2303,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402167</v>
+        <v>121402250</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>98004</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2311,38 +2315,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R18" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2369,12 +2373,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2401,10 +2405,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402171</v>
+        <v>121402199</v>
       </c>
       <c r="B19" t="n">
-        <v>98005</v>
+        <v>98121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2417,34 +2421,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223572</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R19" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2471,12 +2475,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402212</v>
+        <v>121402192</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>105188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402178</v>
+        <v>121402140</v>
       </c>
       <c r="B3" t="n">
-        <v>99109</v>
+        <v>105188</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222467</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402206</v>
+        <v>121402178</v>
       </c>
       <c r="B4" t="n">
-        <v>98119</v>
+        <v>99109</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R4" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402192</v>
+        <v>121402171</v>
       </c>
       <c r="B5" t="n">
-        <v>105188</v>
+        <v>98008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R5" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402166</v>
+        <v>121402250</v>
       </c>
       <c r="B6" t="n">
-        <v>98121</v>
+        <v>98004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R6" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402168</v>
+        <v>121402236</v>
       </c>
       <c r="B7" t="n">
-        <v>98100</v>
+        <v>98002</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R7" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402191</v>
+        <v>121402177</v>
       </c>
       <c r="B8" t="n">
-        <v>97052</v>
+        <v>99137</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,16 +1303,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>222662</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402164</v>
+        <v>121402212</v>
       </c>
       <c r="B9" t="n">
-        <v>98002</v>
+        <v>98016</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R9" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402171</v>
+        <v>121402220</v>
       </c>
       <c r="B10" t="n">
-        <v>98008</v>
+        <v>97052</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R10" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402167</v>
+        <v>121402199</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R11" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402177</v>
+        <v>121402167</v>
       </c>
       <c r="B12" t="n">
-        <v>99137</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222662</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402140</v>
+        <v>121402165</v>
       </c>
       <c r="B13" t="n">
-        <v>105188</v>
+        <v>98119</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402165</v>
+        <v>121402168</v>
       </c>
       <c r="B14" t="n">
-        <v>98119</v>
+        <v>98100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402220</v>
+        <v>121402166</v>
       </c>
       <c r="B15" t="n">
-        <v>97052</v>
+        <v>98121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,34 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R15" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402170</v>
+        <v>121402164</v>
       </c>
       <c r="B16" t="n">
-        <v>98018</v>
+        <v>98002</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,19 +2119,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2201,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402236</v>
+        <v>121402170</v>
       </c>
       <c r="B17" t="n">
-        <v>98002</v>
+        <v>98018</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,34 +2221,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>223597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R17" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2303,10 +2303,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402250</v>
+        <v>121402206</v>
       </c>
       <c r="B18" t="n">
-        <v>98004</v>
+        <v>98119</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,21 +2319,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402199</v>
+        <v>121402191</v>
       </c>
       <c r="B19" t="n">
-        <v>98121</v>
+        <v>97052</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,34 +2421,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R19" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402199</v>
+        <v>121402165</v>
       </c>
       <c r="B11" t="n">
-        <v>98121</v>
+        <v>98119</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R11" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402165</v>
+        <v>121402199</v>
       </c>
       <c r="B13" t="n">
-        <v>98119</v>
+        <v>98121</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R13" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402192</v>
+        <v>121402178</v>
       </c>
       <c r="B2" t="n">
-        <v>105188</v>
+        <v>99109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>222467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R2" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402140</v>
+        <v>121402192</v>
       </c>
       <c r="B3" t="n">
         <v>105188</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R3" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402178</v>
+        <v>121402140</v>
       </c>
       <c r="B4" t="n">
-        <v>99109</v>
+        <v>105188</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222467</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402165</v>
+        <v>121402199</v>
       </c>
       <c r="B11" t="n">
-        <v>98119</v>
+        <v>98121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R11" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402199</v>
+        <v>121402165</v>
       </c>
       <c r="B13" t="n">
-        <v>98121</v>
+        <v>98119</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R13" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402178</v>
+        <v>121402165</v>
       </c>
       <c r="B2" t="n">
-        <v>99109</v>
+        <v>98125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402192</v>
+        <v>121402164</v>
       </c>
       <c r="B3" t="n">
-        <v>105188</v>
+        <v>98008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R3" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402140</v>
+        <v>121402170</v>
       </c>
       <c r="B4" t="n">
-        <v>105188</v>
+        <v>98024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,23 +895,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402171</v>
+        <v>121402168</v>
       </c>
       <c r="B5" t="n">
-        <v>98008</v>
+        <v>98106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223572</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402250</v>
+        <v>121402177</v>
       </c>
       <c r="B6" t="n">
-        <v>98004</v>
+        <v>99143</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1095,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>222662</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1119,14 +1115,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R6" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1153,12 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402236</v>
+        <v>121402238</v>
       </c>
       <c r="B7" t="n">
-        <v>98002</v>
+        <v>98024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,23 +1197,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220093</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402177</v>
+        <v>121402166</v>
       </c>
       <c r="B8" t="n">
-        <v>99137</v>
+        <v>98127</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222662</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1381,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402212</v>
+        <v>121402199</v>
       </c>
       <c r="B9" t="n">
-        <v>98016</v>
+        <v>98127</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402220</v>
+        <v>121402178</v>
       </c>
       <c r="B10" t="n">
-        <v>97052</v>
+        <v>99115</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>222467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R10" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1561,12 +1553,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402199</v>
+        <v>121402171</v>
       </c>
       <c r="B11" t="n">
-        <v>98121</v>
+        <v>98014</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1601,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>223572</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R11" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1663,12 +1655,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402167</v>
+        <v>121402250</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>98010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1699,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R12" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1765,12 +1757,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402165</v>
+        <v>121402206</v>
       </c>
       <c r="B13" t="n">
-        <v>98119</v>
+        <v>98125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,14 +1825,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R13" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1867,12 +1859,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402168</v>
+        <v>121402220</v>
       </c>
       <c r="B14" t="n">
-        <v>98100</v>
+        <v>97058</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,34 +1907,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219811</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R14" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1969,12 +1961,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402166</v>
+        <v>121402236</v>
       </c>
       <c r="B15" t="n">
-        <v>98121</v>
+        <v>98008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,34 +2009,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R15" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2071,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402164</v>
+        <v>121402192</v>
       </c>
       <c r="B16" t="n">
-        <v>98002</v>
+        <v>105194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,34 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R16" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2173,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402170</v>
+        <v>121402191</v>
       </c>
       <c r="B17" t="n">
-        <v>98018</v>
+        <v>97058</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,19 +2213,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2303,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402206</v>
+        <v>121402167</v>
       </c>
       <c r="B18" t="n">
-        <v>98119</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2315,38 +2311,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R18" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2373,12 +2369,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2405,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402191</v>
+        <v>121402140</v>
       </c>
       <c r="B19" t="n">
-        <v>97052</v>
+        <v>105194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402165</v>
+        <v>121402199</v>
       </c>
       <c r="B2" t="n">
-        <v>98125</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R2" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402164</v>
+        <v>121402165</v>
       </c>
       <c r="B3" t="n">
-        <v>98008</v>
+        <v>98126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402170</v>
+        <v>121402220</v>
       </c>
       <c r="B4" t="n">
-        <v>98024</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,30 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R4" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -945,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402168</v>
+        <v>121402166</v>
       </c>
       <c r="B5" t="n">
-        <v>98106</v>
+        <v>98128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402177</v>
+        <v>121402178</v>
       </c>
       <c r="B6" t="n">
-        <v>99143</v>
+        <v>99116</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222662</v>
+        <v>222467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402238</v>
+        <v>121402168</v>
       </c>
       <c r="B7" t="n">
-        <v>98024</v>
+        <v>98107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,30 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R7" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1247,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402166</v>
+        <v>121402238</v>
       </c>
       <c r="B8" t="n">
-        <v>98127</v>
+        <v>98025</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1295,34 +1303,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R8" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1349,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402199</v>
+        <v>121402206</v>
       </c>
       <c r="B9" t="n">
-        <v>98127</v>
+        <v>98126</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402178</v>
+        <v>121402170</v>
       </c>
       <c r="B10" t="n">
-        <v>99115</v>
+        <v>98025</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1499,23 +1503,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222467</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402171</v>
+        <v>121402140</v>
       </c>
       <c r="B11" t="n">
-        <v>98014</v>
+        <v>105195</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1601,21 +1601,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223572</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402250</v>
+        <v>121402236</v>
       </c>
       <c r="B12" t="n">
-        <v>98010</v>
+        <v>98009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402206</v>
+        <v>121402192</v>
       </c>
       <c r="B13" t="n">
-        <v>98125</v>
+        <v>105195</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402220</v>
+        <v>121402164</v>
       </c>
       <c r="B14" t="n">
-        <v>97058</v>
+        <v>98009</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1907,34 +1907,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R14" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402236</v>
+        <v>121402171</v>
       </c>
       <c r="B15" t="n">
-        <v>98008</v>
+        <v>98015</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2009,34 +2009,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>223572</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R15" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402192</v>
+        <v>121402250</v>
       </c>
       <c r="B16" t="n">
-        <v>105194</v>
+        <v>98011</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402191</v>
+        <v>121402167</v>
       </c>
       <c r="B17" t="n">
-        <v>97058</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2209,25 +2209,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402167</v>
+        <v>121402177</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>99144</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2311,25 +2311,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222662</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402140</v>
+        <v>121402191</v>
       </c>
       <c r="B19" t="n">
-        <v>105194</v>
+        <v>97059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402199</v>
+        <v>121402166</v>
       </c>
       <c r="B2" t="n">
         <v>98128</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R2" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402165</v>
+        <v>121402171</v>
       </c>
       <c r="B3" t="n">
-        <v>98126</v>
+        <v>98015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>223572</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402220</v>
+        <v>121402191</v>
       </c>
       <c r="B4" t="n">
         <v>97059</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R4" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402166</v>
+        <v>121402236</v>
       </c>
       <c r="B5" t="n">
-        <v>98128</v>
+        <v>98009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R5" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402178</v>
+        <v>121402170</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>98025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,23 +1099,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222467</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402168</v>
+        <v>121402212</v>
       </c>
       <c r="B7" t="n">
-        <v>98107</v>
+        <v>98023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R7" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1255,12 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402238</v>
+        <v>121402250</v>
       </c>
       <c r="B8" t="n">
-        <v>98025</v>
+        <v>98011</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,19 +1299,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402206</v>
+        <v>121402199</v>
       </c>
       <c r="B9" t="n">
-        <v>98126</v>
+        <v>98128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402170</v>
+        <v>121402140</v>
       </c>
       <c r="B10" t="n">
-        <v>98025</v>
+        <v>105195</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,19 +1503,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1585,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402140</v>
+        <v>121402206</v>
       </c>
       <c r="B11" t="n">
-        <v>105195</v>
+        <v>98126</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1601,34 +1605,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R11" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1655,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1687,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402236</v>
+        <v>121402178</v>
       </c>
       <c r="B12" t="n">
-        <v>98009</v>
+        <v>99116</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1703,34 +1707,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>222467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R12" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1757,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402192</v>
+        <v>121402177</v>
       </c>
       <c r="B13" t="n">
-        <v>105195</v>
+        <v>99144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1805,34 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>222662</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R13" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1859,12 +1863,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402164</v>
+        <v>121402168</v>
       </c>
       <c r="B14" t="n">
-        <v>98009</v>
+        <v>98107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1907,21 +1911,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402171</v>
+        <v>121402220</v>
       </c>
       <c r="B15" t="n">
-        <v>98015</v>
+        <v>97059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2009,34 +2013,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R15" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2063,12 +2067,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402250</v>
+        <v>121402165</v>
       </c>
       <c r="B16" t="n">
-        <v>98011</v>
+        <v>98126</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,34 +2115,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R16" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2165,12 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,10 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402167</v>
+        <v>121402164</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>98009</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2209,25 +2213,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2303,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402177</v>
+        <v>121402192</v>
       </c>
       <c r="B18" t="n">
-        <v>99144</v>
+        <v>105195</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2315,34 +2319,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222662</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R18" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2369,12 +2373,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2401,10 +2405,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402191</v>
+        <v>121402167</v>
       </c>
       <c r="B19" t="n">
-        <v>97059</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2413,25 +2417,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402166</v>
+        <v>121402199</v>
       </c>
       <c r="B2" t="n">
         <v>98128</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R2" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402171</v>
+        <v>121402178</v>
       </c>
       <c r="B3" t="n">
-        <v>98015</v>
+        <v>99116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223572</v>
+        <v>222467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402191</v>
+        <v>121402238</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>98025</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R4" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402236</v>
+        <v>121402250</v>
       </c>
       <c r="B5" t="n">
-        <v>98009</v>
+        <v>98011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402170</v>
+        <v>121402236</v>
       </c>
       <c r="B6" t="n">
-        <v>98025</v>
+        <v>98009</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,30 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R6" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402212</v>
+        <v>121402168</v>
       </c>
       <c r="B7" t="n">
-        <v>98023</v>
+        <v>98107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R7" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402250</v>
+        <v>121402177</v>
       </c>
       <c r="B8" t="n">
-        <v>98011</v>
+        <v>99144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>222662</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1319,14 +1319,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R8" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402199</v>
+        <v>121402167</v>
       </c>
       <c r="B9" t="n">
-        <v>98128</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,38 +1397,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R9" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402140</v>
+        <v>121402220</v>
       </c>
       <c r="B10" t="n">
-        <v>105195</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,34 +1503,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R10" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402206</v>
+        <v>121402192</v>
       </c>
       <c r="B11" t="n">
-        <v>98126</v>
+        <v>105195</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402178</v>
+        <v>121402191</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222467</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402177</v>
+        <v>121402170</v>
       </c>
       <c r="B13" t="n">
-        <v>99144</v>
+        <v>98025</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,23 +1809,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222662</v>
+        <v>223597</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1895,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402168</v>
+        <v>121402206</v>
       </c>
       <c r="B14" t="n">
-        <v>98107</v>
+        <v>98126</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,34 +1907,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219811</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R14" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1961,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402220</v>
+        <v>121402166</v>
       </c>
       <c r="B15" t="n">
-        <v>97059</v>
+        <v>98128</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,34 +2009,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R15" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2067,12 +2063,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402165</v>
+        <v>121402140</v>
       </c>
       <c r="B16" t="n">
-        <v>98126</v>
+        <v>105195</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,21 +2111,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402164</v>
+        <v>121402171</v>
       </c>
       <c r="B17" t="n">
-        <v>98009</v>
+        <v>98015</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,21 +2213,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>223572</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2303,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402192</v>
+        <v>121402164</v>
       </c>
       <c r="B18" t="n">
-        <v>105195</v>
+        <v>98009</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,34 +2315,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R18" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2373,12 +2369,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2405,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402167</v>
+        <v>121402165</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>98126</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2417,25 +2413,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402199</v>
+        <v>121402170</v>
       </c>
       <c r="B2" t="n">
-        <v>98128</v>
+        <v>98025</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>223597</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R2" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,12 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402178</v>
+        <v>121402164</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>98009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +789,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222467</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402238</v>
+        <v>121402236</v>
       </c>
       <c r="B4" t="n">
-        <v>98025</v>
+        <v>98009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,19 +891,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402250</v>
+        <v>121402192</v>
       </c>
       <c r="B5" t="n">
-        <v>98011</v>
+        <v>105195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402236</v>
+        <v>121402140</v>
       </c>
       <c r="B6" t="n">
-        <v>98009</v>
+        <v>105195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,34 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R6" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402168</v>
+        <v>121402220</v>
       </c>
       <c r="B7" t="n">
-        <v>98107</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,34 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R7" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402177</v>
+        <v>121402250</v>
       </c>
       <c r="B8" t="n">
-        <v>99144</v>
+        <v>98011</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222662</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1319,14 +1319,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R8" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402167</v>
+        <v>121402171</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98015</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,25 +1397,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>223572</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402220</v>
+        <v>121402238</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>98025</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,23 +1503,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402192</v>
+        <v>121402178</v>
       </c>
       <c r="B11" t="n">
-        <v>105195</v>
+        <v>99116</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,34 +1601,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>222467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R11" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1659,12 +1655,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402191</v>
+        <v>121402166</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>98128</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402170</v>
+        <v>121402177</v>
       </c>
       <c r="B13" t="n">
-        <v>98025</v>
+        <v>99144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,19 +1805,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223597</v>
+        <v>222662</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402206</v>
+        <v>121402199</v>
       </c>
       <c r="B14" t="n">
-        <v>98126</v>
+        <v>98128</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402166</v>
+        <v>121402167</v>
       </c>
       <c r="B15" t="n">
-        <v>98128</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2005,25 +2005,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402140</v>
+        <v>121402206</v>
       </c>
       <c r="B16" t="n">
-        <v>105195</v>
+        <v>98126</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,34 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R16" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402171</v>
+        <v>121402191</v>
       </c>
       <c r="B17" t="n">
-        <v>98015</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402164</v>
+        <v>121402168</v>
       </c>
       <c r="B18" t="n">
-        <v>98009</v>
+        <v>98107</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402170</v>
+        <v>121402167</v>
       </c>
       <c r="B2" t="n">
-        <v>98025</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,23 +687,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -773,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402164</v>
+        <v>121402220</v>
       </c>
       <c r="B3" t="n">
-        <v>98009</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R3" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -843,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402236</v>
+        <v>121402177</v>
       </c>
       <c r="B4" t="n">
-        <v>98009</v>
+        <v>99152</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>222662</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R4" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -945,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402192</v>
+        <v>121402199</v>
       </c>
       <c r="B5" t="n">
-        <v>105195</v>
+        <v>98136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402140</v>
+        <v>121402164</v>
       </c>
       <c r="B6" t="n">
-        <v>105195</v>
+        <v>98017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402220</v>
+        <v>121402238</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>98033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,23 +1201,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>121402250</v>
       </c>
       <c r="B8" t="n">
-        <v>98011</v>
+        <v>98019</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>121402171</v>
       </c>
       <c r="B9" t="n">
-        <v>98015</v>
+        <v>98023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402238</v>
+        <v>121402236</v>
       </c>
       <c r="B10" t="n">
-        <v>98025</v>
+        <v>98017</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,19 +1503,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1585,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402178</v>
+        <v>121402165</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>98134</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1601,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402166</v>
+        <v>121402206</v>
       </c>
       <c r="B12" t="n">
-        <v>98128</v>
+        <v>98134</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1703,34 +1707,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R12" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1757,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402177</v>
+        <v>121402192</v>
       </c>
       <c r="B13" t="n">
-        <v>99144</v>
+        <v>105203</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1805,34 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222662</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R13" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1859,12 +1863,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402199</v>
+        <v>121402191</v>
       </c>
       <c r="B14" t="n">
-        <v>98128</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1907,34 +1911,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R14" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1961,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1993,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402167</v>
+        <v>121402170</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>98033</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2005,27 +2009,23 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402206</v>
+        <v>121402166</v>
       </c>
       <c r="B16" t="n">
-        <v>98126</v>
+        <v>98136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2111,34 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R16" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402191</v>
+        <v>121402178</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>99124</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>222467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,7 +2302,7 @@
         <v>121402168</v>
       </c>
       <c r="B18" t="n">
-        <v>98107</v>
+        <v>98115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402165</v>
+        <v>121402140</v>
       </c>
       <c r="B19" t="n">
-        <v>98126</v>
+        <v>105203</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121402178</v>
+        <v>62326223</v>
       </c>
       <c r="B2" t="n">
-        <v>99124</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222467</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Västerkälen / NO /, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468694</v>
+        <v>469904</v>
       </c>
       <c r="R2" t="n">
-        <v>7024422</v>
+        <v>7024140</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +741,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1996-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1996-09-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Några 10-tal bestånd kvar. Objekt nr 02:1. De flesta på Kälen 4:2. Ursrpungligen rikligt. Objektet till stor del utplånat i samband med virkesterminalbygge samt anläggande av stickspår från järnvägen. 1989-90. 54 bestånd guckusko flyttade till 70277 / 14293 1989-08-31/-09-01. Obj. omfattar koord Mjölkövergången / 300 - 400 m SO /, Västerkälen /NNO/. Sydväst om järn- vägen, 1000 - 1100 m söder om Bottenmyrbäc- kens utlopp i Näldsjön. VÄSTER om VIRKESTERMINALEN</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,11 +762,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Rikkärr / kalkkärr, Kalkbarrskog, sumpskog,</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -773,19 +779,18 @@
           <t>Bengt Petterson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121402165</v>
+        <v>121402250</v>
       </c>
       <c r="B3" t="n">
-        <v>98134</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R3" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -847,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121402212</v>
+        <v>121402168</v>
       </c>
       <c r="B4" t="n">
-        <v>98031</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R4" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121402220</v>
+        <v>121402166</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R5" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1051,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121402164</v>
+        <v>121402199</v>
       </c>
       <c r="B6" t="n">
-        <v>98017</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R6" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1153,12 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121402206</v>
+        <v>121402164</v>
       </c>
       <c r="B7" t="n">
-        <v>98134</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R7" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1255,12 +1240,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121402192</v>
+        <v>121402236</v>
       </c>
       <c r="B8" t="n">
-        <v>105203</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,50 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121402236</v>
+        <v>121402167</v>
       </c>
       <c r="B9" t="n">
-        <v>98017</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R9" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1459,12 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,15 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121402250</v>
+        <v>121402140</v>
       </c>
       <c r="B10" t="n">
-        <v>98019</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1477,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>504</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster-Kälen, NO om, Jmt</t>
+          <t>Väster-Kälen, N om i myr, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469411</v>
+        <v>468694</v>
       </c>
       <c r="R10" t="n">
-        <v>7024017</v>
+        <v>7024422</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1561,12 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-07-14</t>
+          <t>1989-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,50 +1563,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121402167</v>
+        <v>121402192</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R11" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1663,12 +1628,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,15 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121402177</v>
+        <v>121402191</v>
       </c>
       <c r="B12" t="n">
-        <v>99152</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,16 +1671,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222662</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1797,15 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121402199</v>
+        <v>121402220</v>
       </c>
       <c r="B13" t="n">
-        <v>98136</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,15 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121402191</v>
+        <v>121402165</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2001,15 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121402169</v>
+        <v>121402206</v>
       </c>
       <c r="B15" t="n">
-        <v>98031</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,34 +1962,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster-Kälen, N om i myr, Jmt</t>
+          <t>Väster-Kälen, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468694</v>
+        <v>469411</v>
       </c>
       <c r="R15" t="n">
-        <v>7024422</v>
+        <v>7024017</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2071,12 +2016,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1989-06-20</t>
+          <t>1989-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,15 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121402140</v>
+        <v>121402178</v>
       </c>
       <c r="B16" t="n">
-        <v>105203</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>222467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,15 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121402168</v>
+        <v>121402177</v>
       </c>
       <c r="B17" t="n">
-        <v>98115</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100171</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219811</v>
+        <v>222662</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2307,15 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121402166</v>
+        <v>121402171</v>
       </c>
       <c r="B18" t="n">
-        <v>98136</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>223572</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2409,15 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121402171</v>
+        <v>121402169</v>
       </c>
       <c r="B19" t="n">
-        <v>98023</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223572</v>
+        <v>223591</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2508,6 +2433,103 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121402212</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Väster-Kälen, NO om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>469411</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7024017</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1989-07-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1989-07-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32142-2022 artfynd.xlsx
+++ b/artfynd/A 32142-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62326223</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402166</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402199</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402164</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402140</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402191</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402220</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402165</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402206</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402178</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402177</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402171</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402169</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2530,8 +2625,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121402212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>